--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113705334</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113705336</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,8 +1010,18 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113705532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,50 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113705334</v>
+        <v>135764784</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>92048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Garpenbergs elljusspår, Dlr</t>
+          <t>Kuppdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565179</v>
+        <v>564849</v>
       </c>
       <c r="R2" t="n">
-        <v>6687109</v>
+        <v>6687467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På stående död tall.</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,28 +775,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113705334</t>
+          <t>https://artportalen.se/Sighting/135764784</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113705336</v>
+        <v>113705334</v>
       </c>
       <c r="B3" t="n">
         <v>57950</v>
@@ -836,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564827</v>
+        <v>565179</v>
       </c>
       <c r="R3" t="n">
-        <v>6687308</v>
+        <v>6687109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,16 +902,16 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113705336</t>
+          <t>https://artportalen.se/Sighting/113705334</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113705532</v>
+        <v>113705336</v>
       </c>
       <c r="B4" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Garpenberg, Dlr</t>
+          <t>Garpenbergs elljusspår, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565270</v>
+        <v>564827</v>
       </c>
       <c r="R4" t="n">
-        <v>6687252</v>
+        <v>6687308</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,6 +986,11 @@
           <t>2023-10-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På stående död tall.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1011,6 +1017,2057 @@
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113705336</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135764769</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565162</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6687559</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764769</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135764779</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>564833</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6687368</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764779</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135764786</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>564902</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6687600</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764786</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135764788</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564887</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6687587</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764788</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135764771</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564989</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6687348</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>8 blomstänglar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764771</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135764772</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564981</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6687357</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764772</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135764774</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564930</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6687263</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764774</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135764775</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564899</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6687283</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764775</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135764776</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564839</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6687283</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764776</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135764777</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>564839</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6687327</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764777</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135764780</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>564834</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6687416</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764780</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135764781</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>564836</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6687426</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764781</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135764782</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>564854</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6687445</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764782</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135764783</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>564859</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6687462</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764783</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135764785</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>564835</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6687576</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764785</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135764790</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>565077</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6687506</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764790</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113705532</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Garpenberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>565270</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6687252</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113705532</t>
         </is>
@@ -1021,6 +3078,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135764784</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135764771</v>
       </c>
       <c r="B9" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135764772</v>
       </c>
       <c r="B10" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>135764774</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>135764775</v>
       </c>
       <c r="B12" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>135764776</v>
       </c>
       <c r="B13" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>135764777</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135764780</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135764781</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>135764782</v>
       </c>
       <c r="B17" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135764783</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>135764785</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>135764790</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135764784</v>
+        <v>135757973</v>
       </c>
       <c r="B2" t="n">
         <v>92050</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kuppdammen, Dlr</t>
+          <t>Kolningsvreten, Kolningsvreten, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564849</v>
+        <v>564984</v>
       </c>
       <c r="R2" t="n">
-        <v>6687467</v>
+        <v>6687341</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,67 +765,62 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764784</t>
+          <t>https://artportalen.se/Sighting/135757973</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113705334</v>
+        <v>135764784</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Garpenbergs elljusspår, Dlr</t>
+          <t>Kuppdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565179</v>
+        <v>564849</v>
       </c>
       <c r="R3" t="n">
-        <v>6687109</v>
+        <v>6687467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På stående död tall.</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,28 +877,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113705334</t>
+          <t>https://artportalen.se/Sighting/135764784</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113705336</v>
+        <v>113705334</v>
       </c>
       <c r="B4" t="n">
         <v>57950</v>
@@ -948,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564827</v>
+        <v>565179</v>
       </c>
       <c r="R4" t="n">
-        <v>6687308</v>
+        <v>6687109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,16 +1004,16 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113705336</t>
+          <t>https://artportalen.se/Sighting/113705334</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135764769</v>
+        <v>113705336</v>
       </c>
       <c r="B5" t="n">
-        <v>57977</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,19 +1041,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kuppdammen, Dlr</t>
+          <t>Garpenbergs elljusspår, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565162</v>
+        <v>564827</v>
       </c>
       <c r="R5" t="n">
-        <v>6687559</v>
+        <v>6687308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,22 +1080,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:20</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:20</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På stående död tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,24 +1105,28 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764769</t>
+          <t>https://artportalen.se/Sighting/113705336</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135764779</v>
+        <v>135758426</v>
       </c>
       <c r="B6" t="n">
         <v>57977</v>
@@ -1177,17 +1162,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kuppdammen, Dlr</t>
+          <t>Kolningsvreten, Kolningsvreten, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564833</v>
+        <v>564834</v>
       </c>
       <c r="R6" t="n">
-        <v>6687368</v>
+        <v>6687427</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,19 +1199,9 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,24 +1216,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764779</t>
+          <t>https://artportalen.se/Sighting/135758426</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135764786</v>
+        <v>135764769</v>
       </c>
       <c r="B7" t="n">
         <v>57977</v>
@@ -1289,7 +1264,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1298,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564902</v>
+        <v>565162</v>
       </c>
       <c r="R7" t="n">
-        <v>6687600</v>
+        <v>6687559</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,13 +1344,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764786</t>
+          <t>https://artportalen.se/Sighting/135764769</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135764788</v>
+        <v>135764779</v>
       </c>
       <c r="B8" t="n">
         <v>57977</v>
@@ -1415,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564887</v>
+        <v>564833</v>
       </c>
       <c r="R8" t="n">
-        <v>6687587</v>
+        <v>6687368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,53 +1461,44 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764788</t>
+          <t>https://artportalen.se/Sighting/135764779</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135764771</v>
+        <v>135764786</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1541,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564989</v>
+        <v>564902</v>
       </c>
       <c r="R9" t="n">
-        <v>6687348</v>
+        <v>6687600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,12 +1552,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>8 blomstänglar</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,48 +1578,44 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764771</t>
+          <t>https://artportalen.se/Sighting/135764786</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135764772</v>
+        <v>135764788</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1667,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564981</v>
+        <v>564887</v>
       </c>
       <c r="R10" t="n">
-        <v>6687357</v>
+        <v>6687587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,63 +1695,59 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764772</t>
+          <t>https://artportalen.se/Sighting/135764788</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135764774</v>
+        <v>135757838</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>5181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kuppdammen, Dlr</t>
+          <t>Kolningsvreten, Kolningsvreten, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564930</v>
+        <v>564984</v>
       </c>
       <c r="R11" t="n">
-        <v>6687263</v>
+        <v>6687341</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,19 +1774,9 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>08:54</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>08:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,24 +1791,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764774</t>
+          <t>https://artportalen.se/Sighting/135757838</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135764775</v>
+        <v>135757847</v>
       </c>
       <c r="B12" t="n">
         <v>99276</v>
@@ -1893,34 +1836,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kuppdammen, Dlr</t>
+          <t>Kolningsvreten, Kolningsvreten, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564899</v>
+        <v>564984</v>
       </c>
       <c r="R12" t="n">
-        <v>6687283</v>
+        <v>6687341</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1947,19 +1876,9 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>08:56</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>08:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,24 +1893,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764775</t>
+          <t>https://artportalen.se/Sighting/135757847</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135764776</v>
+        <v>135758253</v>
       </c>
       <c r="B13" t="n">
         <v>99276</v>
@@ -2019,29 +1938,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kuppdammen, Dlr</t>
+          <t>Kolningsvreten, Kolningsvreten, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564839</v>
+        <v>564834</v>
       </c>
       <c r="R13" t="n">
-        <v>6687283</v>
+        <v>6687427</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,19 +1978,9 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,24 +1995,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764776</t>
+          <t>https://artportalen.se/Sighting/135758253</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135764777</v>
+        <v>135764771</v>
       </c>
       <c r="B14" t="n">
         <v>99276</v>
@@ -2142,7 +2042,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2161,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564839</v>
+        <v>564989</v>
       </c>
       <c r="R14" t="n">
-        <v>6687327</v>
+        <v>6687348</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,7 +2096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2206,7 +2106,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>8 blomstänglar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2232,13 +2137,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764777</t>
+          <t>https://artportalen.se/Sighting/135764771</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135764780</v>
+        <v>135764772</v>
       </c>
       <c r="B15" t="n">
         <v>99276</v>
@@ -2268,7 +2173,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2282,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564834</v>
+        <v>564981</v>
       </c>
       <c r="R15" t="n">
-        <v>6687416</v>
+        <v>6687357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2317,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2327,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,13 +2258,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764780</t>
+          <t>https://artportalen.se/Sighting/135764772</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135764781</v>
+        <v>135764774</v>
       </c>
       <c r="B16" t="n">
         <v>99276</v>
@@ -2397,21 +2302,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kuppdammen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564836</v>
+        <v>564930</v>
       </c>
       <c r="R16" t="n">
-        <v>6687426</v>
+        <v>6687263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2443,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2453,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2479,13 +2379,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764781</t>
+          <t>https://artportalen.se/Sighting/135764774</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135764782</v>
+        <v>135764775</v>
       </c>
       <c r="B17" t="n">
         <v>99276</v>
@@ -2523,16 +2423,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kuppdammen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564854</v>
+        <v>564899</v>
       </c>
       <c r="R17" t="n">
-        <v>6687445</v>
+        <v>6687283</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2564,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2574,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2600,13 +2505,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764782</t>
+          <t>https://artportalen.se/Sighting/135764775</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135764783</v>
+        <v>135764776</v>
       </c>
       <c r="B18" t="n">
         <v>99276</v>
@@ -2636,7 +2541,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2650,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564859</v>
+        <v>564839</v>
       </c>
       <c r="R18" t="n">
-        <v>6687462</v>
+        <v>6687283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2685,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2695,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,13 +2626,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764783</t>
+          <t>https://artportalen.se/Sighting/135764776</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135764785</v>
+        <v>135764777</v>
       </c>
       <c r="B19" t="n">
         <v>99276</v>
@@ -2757,7 +2662,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2765,16 +2670,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kuppdammen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564835</v>
+        <v>564839</v>
       </c>
       <c r="R19" t="n">
-        <v>6687576</v>
+        <v>6687327</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2806,7 +2716,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2816,7 +2726,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,13 +2752,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764785</t>
+          <t>https://artportalen.se/Sighting/135764777</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135764790</v>
+        <v>135764780</v>
       </c>
       <c r="B20" t="n">
         <v>99276</v>
@@ -2878,7 +2788,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2892,10 +2802,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565077</v>
+        <v>564834</v>
       </c>
       <c r="R20" t="n">
-        <v>6687506</v>
+        <v>6687416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2927,7 +2837,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2937,7 +2847,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2963,51 +2873,65 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135764790</t>
+          <t>https://artportalen.se/Sighting/135764780</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113705532</v>
+        <v>135764781</v>
       </c>
       <c r="B21" t="n">
-        <v>97983</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Garpenberg, Dlr</t>
+          <t>Kuppdammen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565270</v>
+        <v>564836</v>
       </c>
       <c r="R21" t="n">
-        <v>6687252</v>
+        <v>6687426</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3034,12 +2958,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,20 +2988,606 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764781</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135764782</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>564854</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6687445</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764782</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135764783</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>564859</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6687462</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764783</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135764785</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>564835</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6687576</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764785</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135764790</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kuppdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>565077</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6687506</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764790</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>113705532</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Garpenberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>565270</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6687252</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Lisa Sandberg</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Lisa Sandberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113705532</t>
         </is>
@@ -3095,6 +3615,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135764784</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135758426</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135764769</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135764779</v>
       </c>
       <c r="B8" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>135764786</v>
       </c>
       <c r="B9" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135764788</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135757838</v>
       </c>
       <c r="B11" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135764771</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>135764772</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>135764774</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135764775</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135764776</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135764777</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135764780</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>135764781</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135764782</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135764783</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135764785</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135764790</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135764784</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135764771</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>135764772</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>135764774</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135764775</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135764776</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135764777</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135764780</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>135764781</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135764782</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135764783</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135764785</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135764790</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135764784</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135764771</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>135764772</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>135764774</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135764775</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135764776</v>
       </c>
       <c r="B18" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135764777</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135764780</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>135764781</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135764782</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135764783</v>
       </c>
       <c r="B23" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135764785</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135764790</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135764784</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135758426</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135764769</v>
       </c>
       <c r="B7" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135764779</v>
       </c>
       <c r="B8" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>135764786</v>
       </c>
       <c r="B9" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135764788</v>
       </c>
       <c r="B10" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135764771</v>
       </c>
       <c r="B14" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>135764772</v>
       </c>
       <c r="B15" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>135764774</v>
       </c>
       <c r="B16" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135764775</v>
       </c>
       <c r="B17" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135764776</v>
       </c>
       <c r="B18" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135764777</v>
       </c>
       <c r="B19" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135764780</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>135764781</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135764782</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135764783</v>
       </c>
       <c r="B23" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135764785</v>
       </c>
       <c r="B24" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135764790</v>
       </c>
       <c r="B25" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135764784</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135758426</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135764769</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135764779</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>135764786</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135764788</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135764771</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>135764772</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>135764774</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135764775</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135764776</v>
       </c>
       <c r="B18" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135764777</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135764780</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>135764781</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135764782</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135764783</v>
       </c>
       <c r="B23" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135764785</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135764790</v>
       </c>
       <c r="B25" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135764784</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135758426</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135764769</v>
       </c>
       <c r="B7" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135764779</v>
       </c>
       <c r="B8" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>135764786</v>
       </c>
       <c r="B9" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135764788</v>
       </c>
       <c r="B10" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135764771</v>
       </c>
       <c r="B14" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>135764772</v>
       </c>
       <c r="B15" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>135764774</v>
       </c>
       <c r="B16" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135764775</v>
       </c>
       <c r="B17" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135764776</v>
       </c>
       <c r="B18" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135764777</v>
       </c>
       <c r="B19" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135764780</v>
       </c>
       <c r="B20" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>135764781</v>
       </c>
       <c r="B21" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135764782</v>
       </c>
       <c r="B22" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135764783</v>
       </c>
       <c r="B23" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135764785</v>
       </c>
       <c r="B24" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135764790</v>
       </c>
       <c r="B25" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135764784</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135764771</v>
       </c>
       <c r="B14" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>135764772</v>
       </c>
       <c r="B15" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>135764774</v>
       </c>
       <c r="B16" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135764775</v>
       </c>
       <c r="B17" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135764776</v>
       </c>
       <c r="B18" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135764777</v>
       </c>
       <c r="B19" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135764780</v>
       </c>
       <c r="B20" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>135764781</v>
       </c>
       <c r="B21" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135764782</v>
       </c>
       <c r="B22" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135764783</v>
       </c>
       <c r="B23" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135764785</v>
       </c>
       <c r="B24" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135764790</v>
       </c>
       <c r="B25" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135764784</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135758426</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135764769</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135764779</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>135764786</v>
       </c>
       <c r="B9" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135764788</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135764771</v>
       </c>
       <c r="B14" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>135764772</v>
       </c>
       <c r="B15" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>135764774</v>
       </c>
       <c r="B16" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135764775</v>
       </c>
       <c r="B17" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135764776</v>
       </c>
       <c r="B18" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135764777</v>
       </c>
       <c r="B19" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135764780</v>
       </c>
       <c r="B20" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>135764781</v>
       </c>
       <c r="B21" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135764782</v>
       </c>
       <c r="B22" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135764783</v>
       </c>
       <c r="B23" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135764785</v>
       </c>
       <c r="B24" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135764790</v>
       </c>
       <c r="B25" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135758426</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29521-2026 artfynd.xlsx
+++ b/artfynd/A 29521-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135757973</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135757847</v>
       </c>
       <c r="B12" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>135758253</v>
       </c>
       <c r="B13" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
